--- a/monitor_xlsx/20260225.xlsx
+++ b/monitor_xlsx/20260225.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2065,112 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>漢唐</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4697</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>737</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H21" t="n">
+        <v>201</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-272</v>
+      </c>
+      <c r="J21" t="n">
+        <v>120</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2406</v>
+      </c>
+      <c r="L21" t="n">
+        <v>12109</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-47589</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1450</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4862</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1794</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1359</v>
+      </c>
+      <c r="J22" t="n">
+        <v>59</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1780</v>
+      </c>
+      <c r="L22" t="n">
+        <v>9668</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-140150</v>
+      </c>
+      <c r="N22" t="n">
+        <v>17.67</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260225.xlsx
+++ b/monitor_xlsx/20260225.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V22"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2171,165 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6640</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>962</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>826</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-96</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-85</v>
+      </c>
+      <c r="J23" t="n">
+        <v>37</v>
+      </c>
+      <c r="K23" t="n">
+        <v>24</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>主力積極賣出</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>624</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2040</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>2060</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-93</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-299</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-698</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>主力積極買進</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1255</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3934</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-614</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-1102</v>
+      </c>
+      <c r="H25" t="n">
+        <v>405</v>
+      </c>
+      <c r="I25" t="n">
+        <v>865</v>
+      </c>
+      <c r="J25" t="n">
+        <v>64</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1544</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5413</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-106280</v>
+      </c>
+      <c r="N25" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>偏空</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>

--- a/monitor_xlsx/20260225.xlsx
+++ b/monitor_xlsx/20260225.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2330,6 +2330,59 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3030</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>德律</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>203.5</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3691</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-174</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1850</v>
+      </c>
+      <c r="H26" t="n">
+        <v>46</v>
+      </c>
+      <c r="I26" t="n">
+        <v>30</v>
+      </c>
+      <c r="J26" t="n">
+        <v>111</v>
+      </c>
+      <c r="K26" t="n">
+        <v>6329</v>
+      </c>
+      <c r="L26" t="n">
+        <v>29911</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-58851</v>
+      </c>
+      <c r="N26" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>偏多</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
